--- a/loss-time/outputs/Loss_time_05-10_den_20-10.xlsx
+++ b/loss-time/outputs/Loss_time_05-10_den_20-10.xlsx
@@ -39,8 +39,8 @@
     <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">'Loss time 15-10'!$A$2:$Q$39</definedName>
     <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">'Loss time 16-10'!$A$2:$Q$40</definedName>
     <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">'Loss time 17-10'!$A$2:$Q$40</definedName>
-    <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'Loss time 19-10'!$A$2:$Q$40</definedName>
-    <definedName function="false" hidden="true" localSheetId="13" name="_xlnm._FilterDatabase" vbProcedure="false">'Loss time 20-10'!$A$2:$Q$39</definedName>
+    <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'Loss time 19-10'!$A$2:$Q$42</definedName>
+    <definedName function="false" hidden="true" localSheetId="13" name="_xlnm._FilterDatabase" vbProcedure="false">'Loss time 20-10'!$A$2:$Q$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4513" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4617" uniqueCount="316">
   <si>
     <t xml:space="preserve">LOSS TIME WHITE WOOD - 05/10/2026</t>
   </si>
@@ -755,6 +755,12 @@
     <t xml:space="preserve">A2 ngày 3/12 - nhóm 16/10</t>
   </si>
   <si>
+    <t xml:space="preserve">HC mới- 50% hiệu suất- 2 tuần-19/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 ngày 1/12 - nhóm 19/10</t>
+  </si>
+  <si>
     <t xml:space="preserve">TỔNG HỢP LOSS TIME LABOR (GIỜ CÔNG)</t>
   </si>
   <si>
@@ -863,13 +869,19 @@
     <t xml:space="preserve">Ngày cuối A2 (không tính CN)</t>
   </si>
   <si>
-    <t xml:space="preserve">16/10</t>
+    <t xml:space="preserve">20/10</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
   </si>
   <si>
+    <t xml:space="preserve">19/10</t>
+  </si>
+  <si>
     <t xml:space="preserve">A2 ngày 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/10</t>
   </si>
   <si>
     <t xml:space="preserve">A2 ngày 2</t>
@@ -977,7 +989,7 @@
     <t xml:space="preserve">Ngày 09/10 có 8 nhân viên mới (Assembly 6, Raw Cutting Panel 2; lấy theo P22 đã nhập trên hệ thống), A2 bắt đầu từ 10/10. Ngày 10/10 chưa thấy có nhân viên mới (chờ xác nhận).</t>
   </si>
   <si>
-    <t xml:space="preserve">Chủ nhật 11/10 không làm nên không tính vào số ngày A2. Ngày 12/10 có 3 nhân viên mới (Assembly 2, Raw Cutting Panel 1), A2 bắt đầu từ 13/10. Ngày 13/10 có 7 nhân viên mới (Assembly 2, Raw Cutting Panel 4, Machining 1), ngày 14/10 có 1 (Assembly), ngày 15/10 có 4 (Assembly), ngày 16/10 có 1 nhân viên mới (Assembly, theo dòng P22 đã nhập trên hệ thống), ngày 17/10, 19/10 và 20/10 không có nhân viên mới (người dùng báo). Thứ Bảy 17/10 không tăng ca (P26 và P20 Assembly 7:30-15:30). Thứ Hai 19/10 và Thứ Ba 20/10 ghi theo mẫu ngày thường có tăng ca đến 20:00 (cần xác nhận). Tài xế xe nâng (Machining 12/10, nhóm IDL-Forklift) không tính theo yêu cầu.</t>
+    <t xml:space="preserve">Chủ nhật 11/10 không làm nên không tính vào số ngày A2. Ngày 12/10 có 3 nhân viên mới (Assembly 2, Raw Cutting Panel 1), A2 bắt đầu từ 13/10. Ngày 13/10 có 7 nhân viên mới (Assembly 2, Raw Cutting Panel 4, Machining 1), ngày 14/10 có 1 (Assembly), ngày 15/10 có 4 (Assembly), ngày 16/10 có 1 nhân viên mới (Assembly, theo dòng P22 đã nhập trên hệ thống), ngày 17/10 không có nhân viên mới. Ngày 19/10 có 3 nhân viên mới (Assembly 2, Machining 1; người ghi "0" ở cột CT/TV vẫn tính vào HC), ngày 20/10 có 6 (Assembly 4, gồm 2 người dưới Mr.Dũng-Inlay; Machining 2). Thứ Bảy 17/10 không tăng ca (P26 và P20 Assembly 7:30-15:30). Thứ Hai 19/10 và Thứ Ba 20/10 ghi theo mẫu ngày thường có tăng ca đến 20:00 (cần xác nhận). Tài xế xe nâng (Machining 12/10, nhóm IDL-Forklift) không tính theo yêu cầu.</t>
   </si>
   <si>
     <t xml:space="preserve">Thứ Bảy 10/10 không tăng ca: P26 và P20 Assembly ghi 7:30-15:30 (sớm 30 phút so với ca ngày thường 7:30-16:00); 4 dòng P20 ngắn ghi 7:00-7:30 theo mặc định, chờ xác nhận.</t>
@@ -9198,7 +9210,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -10227,99 +10239,95 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="str">
+      <c r="A23" s="8" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B23,21)</f>
         <v>W43</v>
       </c>
-      <c r="B23" s="14" t="n">
+      <c r="B23" s="9" t="n">
         <v>46314</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13" t="s">
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="J23" s="13" t="s">
+      <c r="H23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K23" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="M23" s="16" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="N23" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O23" s="17" t="n">
+      <c r="K23" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L23" s="10"/>
+      <c r="M23" s="11" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="O23" s="12" t="n">
         <f aca="false">(N23-M23)*24</f>
-        <v>4.5</v>
-      </c>
-      <c r="P23" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q23" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="12" t="n">
         <f aca="false">P23*O23</f>
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="str">
+      <c r="A24" s="8" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B24,21)</f>
         <v>W43</v>
       </c>
-      <c r="B24" s="14" t="n">
+      <c r="B24" s="9" t="n">
         <v>46314</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="J24" s="13" t="s">
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K24" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="L24" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="M24" s="16" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="N24" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O24" s="17" t="n">
+      <c r="K24" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L24" s="10"/>
+      <c r="M24" s="11" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="O24" s="12" t="n">
         <f aca="false">(N24-M24)*24</f>
-        <v>4.5</v>
-      </c>
-      <c r="P24" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q24" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="12" t="n">
         <f aca="false">P24*O24</f>
-        <v>31.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10335,7 +10343,7 @@
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>52</v>
@@ -10347,10 +10355,10 @@
         <v>50</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M25" s="16" t="n">
         <v>0.3125</v>
@@ -10363,11 +10371,11 @@
         <v>4.5</v>
       </c>
       <c r="P25" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q25" s="17" t="n">
         <f aca="false">P25*O25</f>
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10383,7 +10391,7 @@
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
       <c r="G26" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>52</v>
@@ -10411,11 +10419,11 @@
         <v>4.5</v>
       </c>
       <c r="P26" s="13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q26" s="17" t="n">
         <f aca="false">P26*O26</f>
-        <v>13.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10431,7 +10439,7 @@
       <c r="E27" s="13"/>
       <c r="F27" s="13"/>
       <c r="G27" s="13" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>52</v>
@@ -10443,10 +10451,10 @@
         <v>50</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M27" s="16" t="n">
         <v>0.3125</v>
@@ -10459,11 +10467,11 @@
         <v>4.5</v>
       </c>
       <c r="P27" s="13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q27" s="17" t="n">
         <f aca="false">P27*O27</f>
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10479,7 +10487,7 @@
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
       <c r="G28" s="13" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>52</v>
@@ -10491,10 +10499,10 @@
         <v>50</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M28" s="16" t="n">
         <v>0.3125</v>
@@ -10507,11 +10515,11 @@
         <v>4.5</v>
       </c>
       <c r="P28" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" s="17" t="n">
         <f aca="false">P28*O28</f>
-        <v>9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10527,7 +10535,7 @@
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
       <c r="G29" s="13" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>52</v>
@@ -10539,10 +10547,10 @@
         <v>50</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M29" s="16" t="n">
         <v>0.3125</v>
@@ -10555,11 +10563,11 @@
         <v>4.5</v>
       </c>
       <c r="P29" s="13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q29" s="17" t="n">
         <f aca="false">P29*O29</f>
-        <v>4.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10575,7 +10583,7 @@
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
       <c r="G30" s="13" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>52</v>
@@ -10587,10 +10595,10 @@
         <v>50</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M30" s="16" t="n">
         <v>0.3125</v>
@@ -10603,11 +10611,11 @@
         <v>4.5</v>
       </c>
       <c r="P30" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="17" t="n">
         <f aca="false">P30*O30</f>
-        <v>13.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10623,7 +10631,7 @@
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
       <c r="G31" s="13" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>52</v>
@@ -10635,10 +10643,10 @@
         <v>50</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M31" s="16" t="n">
         <v>0.3125</v>
@@ -10651,11 +10659,11 @@
         <v>4.5</v>
       </c>
       <c r="P31" s="13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="17" t="n">
         <f aca="false">P31*O31</f>
-        <v>27</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10671,7 +10679,7 @@
       <c r="E32" s="13"/>
       <c r="F32" s="13"/>
       <c r="G32" s="13" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>52</v>
@@ -10683,10 +10691,10 @@
         <v>50</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M32" s="16" t="n">
         <v>0.3125</v>
@@ -10699,11 +10707,11 @@
         <v>4.5</v>
       </c>
       <c r="P32" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32" s="17" t="n">
         <f aca="false">P32*O32</f>
-        <v>9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10731,10 +10739,10 @@
         <v>50</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M33" s="16" t="n">
         <v>0.3125</v>
@@ -10747,11 +10755,11 @@
         <v>4.5</v>
       </c>
       <c r="P33" s="13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q33" s="17" t="n">
         <f aca="false">P33*O33</f>
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10779,10 +10787,10 @@
         <v>50</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M34" s="16" t="n">
         <v>0.3125</v>
@@ -10795,11 +10803,11 @@
         <v>4.5</v>
       </c>
       <c r="P34" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="17" t="n">
         <f aca="false">P34*O34</f>
-        <v>4.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10827,10 +10835,10 @@
         <v>50</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M35" s="16" t="n">
         <v>0.3125</v>
@@ -10875,10 +10883,10 @@
         <v>50</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="L36" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M36" s="16" t="n">
         <v>0.3125</v>
@@ -10891,11 +10899,11 @@
         <v>4.5</v>
       </c>
       <c r="P36" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="17" t="n">
         <f aca="false">P36*O36</f>
-        <v>18</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10911,7 +10919,7 @@
       <c r="E37" s="13"/>
       <c r="F37" s="13"/>
       <c r="G37" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>52</v>
@@ -10939,11 +10947,11 @@
         <v>4.5</v>
       </c>
       <c r="P37" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="17" t="n">
         <f aca="false">P37*O37</f>
-        <v>4.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10959,7 +10967,7 @@
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
       <c r="G38" s="13" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>52</v>
@@ -10971,10 +10979,10 @@
         <v>50</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="L38" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M38" s="16" t="n">
         <v>0.3125</v>
@@ -10987,11 +10995,11 @@
         <v>4.5</v>
       </c>
       <c r="P38" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q38" s="17" t="n">
         <f aca="false">P38*O38</f>
-        <v>4.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11007,7 +11015,7 @@
       <c r="E39" s="13"/>
       <c r="F39" s="13"/>
       <c r="G39" s="13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H39" s="13" t="s">
         <v>52</v>
@@ -11019,10 +11027,10 @@
         <v>50</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="M39" s="16" t="n">
         <v>0.3125</v>
@@ -11035,11 +11043,11 @@
         <v>4.5</v>
       </c>
       <c r="P39" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="17" t="n">
         <f aca="false">P39*O39</f>
-        <v>18</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11067,10 +11075,10 @@
         <v>50</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M40" s="16" t="n">
         <v>0.3125</v>
@@ -11091,21 +11099,117 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P41" s="18" t="s">
+      <c r="A41" s="13" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B41,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="M41" s="16" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N41" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O41" s="17" t="n">
+        <f aca="false">(N41-M41)*24</f>
+        <v>4.5</v>
+      </c>
+      <c r="P41" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q41" s="17" t="n">
+        <f aca="false">P41*O41</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B42,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="M42" s="16" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N42" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O42" s="17" t="n">
+        <f aca="false">(N42-M42)*24</f>
+        <v>4.5</v>
+      </c>
+      <c r="P42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="17" t="n">
+        <f aca="false">P42*O42</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P43" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="Q41" s="19" t="n">
-        <f aca="false">SUM(Q3:Q40)</f>
-        <v>524</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="20" t="s">
+      <c r="Q43" s="19" t="n">
+        <f aca="false">SUM(Q3:Q42)</f>
+        <v>548</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q40"/>
+  <autoFilter ref="A2:Q42"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -11122,7 +11226,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -12151,99 +12255,95 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="str">
+      <c r="A23" s="8" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B23,21)</f>
         <v>W43</v>
       </c>
-      <c r="B23" s="14" t="n">
+      <c r="B23" s="9" t="n">
         <v>46315</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13" t="s">
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="J23" s="13" t="s">
+      <c r="H23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K23" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="M23" s="16" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="N23" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O23" s="17" t="n">
+      <c r="K23" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L23" s="10"/>
+      <c r="M23" s="11" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="O23" s="12" t="n">
         <f aca="false">(N23-M23)*24</f>
-        <v>4.5</v>
-      </c>
-      <c r="P23" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q23" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="12" t="n">
         <f aca="false">P23*O23</f>
-        <v>31.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="str">
+      <c r="A24" s="8" t="str">
         <f aca="false">"W"&amp;WEEKNUM(B24,21)</f>
         <v>W43</v>
       </c>
-      <c r="B24" s="14" t="n">
+      <c r="B24" s="9" t="n">
         <v>46315</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="J24" s="13" t="s">
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K24" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="L24" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="M24" s="16" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="N24" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O24" s="17" t="n">
+      <c r="K24" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L24" s="10"/>
+      <c r="M24" s="11" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="O24" s="12" t="n">
         <f aca="false">(N24-M24)*24</f>
-        <v>4.5</v>
-      </c>
-      <c r="P24" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q24" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" s="12" t="n">
         <f aca="false">P24*O24</f>
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12259,7 +12359,7 @@
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>52</v>
@@ -12287,11 +12387,11 @@
         <v>4.5</v>
       </c>
       <c r="P25" s="13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q25" s="17" t="n">
         <f aca="false">P25*O25</f>
-        <v>13.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12307,7 +12407,7 @@
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
       <c r="G26" s="13" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>52</v>
@@ -12319,10 +12419,10 @@
         <v>50</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M26" s="16" t="n">
         <v>0.3125</v>
@@ -12335,11 +12435,11 @@
         <v>4.5</v>
       </c>
       <c r="P26" s="13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q26" s="17" t="n">
         <f aca="false">P26*O26</f>
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12355,7 +12455,7 @@
       <c r="E27" s="13"/>
       <c r="F27" s="13"/>
       <c r="G27" s="13" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>52</v>
@@ -12367,10 +12467,10 @@
         <v>50</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M27" s="16" t="n">
         <v>0.3125</v>
@@ -12383,11 +12483,11 @@
         <v>4.5</v>
       </c>
       <c r="P27" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="17" t="n">
         <f aca="false">P27*O27</f>
-        <v>9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12403,7 +12503,7 @@
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
       <c r="G28" s="13" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>52</v>
@@ -12415,10 +12515,10 @@
         <v>50</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M28" s="16" t="n">
         <v>0.3125</v>
@@ -12431,11 +12531,11 @@
         <v>4.5</v>
       </c>
       <c r="P28" s="13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q28" s="17" t="n">
         <f aca="false">P28*O28</f>
-        <v>4.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12451,7 +12551,7 @@
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
       <c r="G29" s="13" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>52</v>
@@ -12463,10 +12563,10 @@
         <v>50</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M29" s="16" t="n">
         <v>0.3125</v>
@@ -12479,11 +12579,11 @@
         <v>4.5</v>
       </c>
       <c r="P29" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="17" t="n">
         <f aca="false">P29*O29</f>
-        <v>13.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12499,7 +12599,7 @@
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
       <c r="G30" s="13" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>52</v>
@@ -12511,10 +12611,10 @@
         <v>50</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M30" s="16" t="n">
         <v>0.3125</v>
@@ -12527,11 +12627,11 @@
         <v>4.5</v>
       </c>
       <c r="P30" s="13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="17" t="n">
         <f aca="false">P30*O30</f>
-        <v>27</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12547,7 +12647,7 @@
       <c r="E31" s="13"/>
       <c r="F31" s="13"/>
       <c r="G31" s="13" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>52</v>
@@ -12559,10 +12659,10 @@
         <v>50</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M31" s="16" t="n">
         <v>0.3125</v>
@@ -12575,11 +12675,11 @@
         <v>4.5</v>
       </c>
       <c r="P31" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="17" t="n">
         <f aca="false">P31*O31</f>
-        <v>9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12607,10 +12707,10 @@
         <v>50</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M32" s="16" t="n">
         <v>0.3125</v>
@@ -12623,11 +12723,11 @@
         <v>4.5</v>
       </c>
       <c r="P32" s="13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q32" s="17" t="n">
         <f aca="false">P32*O32</f>
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12655,10 +12755,10 @@
         <v>50</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M33" s="16" t="n">
         <v>0.3125</v>
@@ -12671,11 +12771,11 @@
         <v>4.5</v>
       </c>
       <c r="P33" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="17" t="n">
         <f aca="false">P33*O33</f>
-        <v>4.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12703,10 +12803,10 @@
         <v>50</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M34" s="16" t="n">
         <v>0.3125</v>
@@ -12751,10 +12851,10 @@
         <v>50</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M35" s="16" t="n">
         <v>0.3125</v>
@@ -12767,11 +12867,11 @@
         <v>4.5</v>
       </c>
       <c r="P35" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="17" t="n">
         <f aca="false">P35*O35</f>
-        <v>18</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12787,7 +12887,7 @@
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
       <c r="G36" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>52</v>
@@ -12815,11 +12915,11 @@
         <v>4.5</v>
       </c>
       <c r="P36" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q36" s="17" t="n">
         <f aca="false">P36*O36</f>
-        <v>4.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12835,7 +12935,7 @@
       <c r="E37" s="13"/>
       <c r="F37" s="13"/>
       <c r="G37" s="13" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>52</v>
@@ -12847,10 +12947,10 @@
         <v>50</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M37" s="16" t="n">
         <v>0.3125</v>
@@ -12863,11 +12963,11 @@
         <v>4.5</v>
       </c>
       <c r="P37" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q37" s="17" t="n">
         <f aca="false">P37*O37</f>
-        <v>4.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12883,7 +12983,7 @@
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
       <c r="G38" s="13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>52</v>
@@ -12895,10 +12995,10 @@
         <v>50</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="L38" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M38" s="16" t="n">
         <v>0.3125</v>
@@ -12911,11 +13011,11 @@
         <v>4.5</v>
       </c>
       <c r="P38" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q38" s="17" t="n">
         <f aca="false">P38*O38</f>
-        <v>18</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12943,10 +13043,10 @@
         <v>50</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M39" s="16" t="n">
         <v>0.3125</v>
@@ -12967,21 +13067,213 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P40" s="18" t="s">
+      <c r="A40" s="13" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B40,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="L40" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="M40" s="16" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N40" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O40" s="17" t="n">
+        <f aca="false">(N40-M40)*24</f>
+        <v>4.5</v>
+      </c>
+      <c r="P40" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q40" s="17" t="n">
+        <f aca="false">P40*O40</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B41,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="M41" s="16" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N41" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O41" s="17" t="n">
+        <f aca="false">(N41-M41)*24</f>
+        <v>4.5</v>
+      </c>
+      <c r="P41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="17" t="n">
+        <f aca="false">P41*O41</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B42,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="M42" s="16" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N42" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O42" s="17" t="n">
+        <f aca="false">(N42-M42)*24</f>
+        <v>4.5</v>
+      </c>
+      <c r="P42" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" s="17" t="n">
+        <f aca="false">P42*O42</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="str">
+        <f aca="false">"W"&amp;WEEKNUM(B43,21)</f>
+        <v>W43</v>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="M43" s="16" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N43" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O43" s="17" t="n">
+        <f aca="false">(N43-M43)*24</f>
+        <v>4.5</v>
+      </c>
+      <c r="P43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="17" t="n">
+        <f aca="false">P43*O43</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P44" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="Q40" s="19" t="n">
-        <f aca="false">SUM(Q3:Q39)</f>
-        <v>497</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="20" t="s">
+      <c r="Q44" s="19" t="n">
+        <f aca="false">SUM(Q3:Q43)</f>
+        <v>558.5</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="20" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q39"/>
+  <autoFilter ref="A2:Q43"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -13008,12 +13300,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13021,7 +13313,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
@@ -13042,7 +13334,7 @@
         <v>72</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>75</v>
@@ -13248,7 +13540,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13256,7 +13548,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>18</v>
@@ -13277,7 +13569,7 @@
         <v>72</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>75</v>
@@ -13483,7 +13775,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13491,7 +13783,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>18</v>
@@ -13512,7 +13804,7 @@
         <v>72</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>75</v>
@@ -13718,7 +14010,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13726,7 +14018,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>18</v>
@@ -13747,7 +14039,7 @@
         <v>72</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>75</v>
@@ -13953,7 +14245,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13961,7 +14253,7 @@
         <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>18</v>
@@ -13982,7 +14274,7 @@
         <v>72</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>75</v>
@@ -14188,7 +14480,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="18" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14196,7 +14488,7 @@
         <v>8</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>18</v>
@@ -14217,7 +14509,7 @@
         <v>72</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>75</v>
@@ -14423,7 +14715,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="18" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14431,7 +14723,7 @@
         <v>8</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>18</v>
@@ -14452,7 +14744,7 @@
         <v>72</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>75</v>
@@ -14658,7 +14950,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="18" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14666,7 +14958,7 @@
         <v>8</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>18</v>
@@ -14687,7 +14979,7 @@
         <v>72</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>75</v>
@@ -14893,7 +15185,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="18" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14901,7 +15193,7 @@
         <v>8</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>18</v>
@@ -14922,7 +15214,7 @@
         <v>72</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>75</v>
@@ -15128,7 +15420,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="18" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15136,7 +15428,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>18</v>
@@ -15157,7 +15449,7 @@
         <v>72</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>75</v>
@@ -15363,7 +15655,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="18" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15371,7 +15663,7 @@
         <v>8</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>18</v>
@@ -15392,7 +15684,7 @@
         <v>72</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>75</v>
@@ -15598,7 +15890,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="18" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15606,7 +15898,7 @@
         <v>8</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>18</v>
@@ -15627,7 +15919,7 @@
         <v>72</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>75</v>
@@ -15833,7 +16125,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="18" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15841,7 +16133,7 @@
         <v>8</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>18</v>
@@ -15862,7 +16154,7 @@
         <v>72</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>75</v>
@@ -15876,31 +16168,31 @@
         <v>20</v>
       </c>
       <c r="C113" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A113,'Loss time 19-10'!$G$3:$G$40,C$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A113,'Loss time 19-10'!$G$3:$G$42,C$112)</f>
         <v>3.5</v>
       </c>
       <c r="D113" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A113,'Loss time 19-10'!$G$3:$G$40,D$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A113,'Loss time 19-10'!$G$3:$G$42,D$112)</f>
         <v>9</v>
       </c>
       <c r="E113" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A113,'Loss time 19-10'!$G$3:$G$40,E$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A113,'Loss time 19-10'!$G$3:$G$42,E$112)</f>
         <v>9.5</v>
       </c>
       <c r="F113" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A113,'Loss time 19-10'!$G$3:$G$40,F$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A113,'Loss time 19-10'!$G$3:$G$42,F$112)</f>
         <v>25</v>
       </c>
       <c r="G113" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A113,'Loss time 19-10'!$G$3:$G$40,G$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A113,'Loss time 19-10'!$G$3:$G$42,G$112)</f>
         <v>0</v>
       </c>
       <c r="H113" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A113,'Loss time 19-10'!$G$3:$G$40,H$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A113,'Loss time 19-10'!$G$3:$G$42,H$112)</f>
         <v>0</v>
       </c>
       <c r="I113" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A113,'Loss time 19-10'!$G$3:$G$40,I$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A113,'Loss time 19-10'!$G$3:$G$42,I$112)</f>
         <v>0</v>
       </c>
       <c r="J113" s="24" t="n">
@@ -15916,31 +16208,31 @@
         <v>31</v>
       </c>
       <c r="C114" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A114,'Loss time 19-10'!$G$3:$G$40,C$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A114,'Loss time 19-10'!$G$3:$G$42,C$112)</f>
         <v>12.5</v>
       </c>
       <c r="D114" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A114,'Loss time 19-10'!$G$3:$G$40,D$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A114,'Loss time 19-10'!$G$3:$G$42,D$112)</f>
         <v>112.5</v>
       </c>
       <c r="E114" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A114,'Loss time 19-10'!$G$3:$G$40,E$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A114,'Loss time 19-10'!$G$3:$G$42,E$112)</f>
         <v>75</v>
       </c>
       <c r="F114" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A114,'Loss time 19-10'!$G$3:$G$40,F$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A114,'Loss time 19-10'!$G$3:$G$42,F$112)</f>
         <v>25</v>
       </c>
       <c r="G114" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A114,'Loss time 19-10'!$G$3:$G$40,G$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A114,'Loss time 19-10'!$G$3:$G$42,G$112)</f>
         <v>0</v>
       </c>
       <c r="H114" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A114,'Loss time 19-10'!$G$3:$G$40,H$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A114,'Loss time 19-10'!$G$3:$G$42,H$112)</f>
         <v>0</v>
       </c>
       <c r="I114" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A114,'Loss time 19-10'!$G$3:$G$40,I$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A114,'Loss time 19-10'!$G$3:$G$42,I$112)</f>
         <v>0</v>
       </c>
       <c r="J114" s="24" t="n">
@@ -15956,36 +16248,36 @@
         <v>49</v>
       </c>
       <c r="C115" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A115,'Loss time 19-10'!$G$3:$G$40,C$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A115,'Loss time 19-10'!$G$3:$G$42,C$112)</f>
         <v>0</v>
       </c>
       <c r="D115" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A115,'Loss time 19-10'!$G$3:$G$40,D$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A115,'Loss time 19-10'!$G$3:$G$42,D$112)</f>
         <v>0</v>
       </c>
       <c r="E115" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A115,'Loss time 19-10'!$G$3:$G$40,E$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A115,'Loss time 19-10'!$G$3:$G$42,E$112)</f>
+        <v>8</v>
+      </c>
+      <c r="F115" s="23" t="n">
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A115,'Loss time 19-10'!$G$3:$G$42,F$112)</f>
+        <v>16</v>
+      </c>
+      <c r="G115" s="23" t="n">
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A115,'Loss time 19-10'!$G$3:$G$42,G$112)</f>
         <v>0</v>
       </c>
-      <c r="F115" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A115,'Loss time 19-10'!$G$3:$G$40,F$112)</f>
+      <c r="H115" s="23" t="n">
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A115,'Loss time 19-10'!$G$3:$G$42,H$112)</f>
         <v>0</v>
       </c>
-      <c r="G115" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A115,'Loss time 19-10'!$G$3:$G$40,G$112)</f>
-        <v>0</v>
-      </c>
-      <c r="H115" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A115,'Loss time 19-10'!$G$3:$G$40,H$112)</f>
-        <v>0</v>
-      </c>
       <c r="I115" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A115,'Loss time 19-10'!$G$3:$G$40,I$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A115,'Loss time 19-10'!$G$3:$G$42,I$112)</f>
         <v>0</v>
       </c>
       <c r="J115" s="24" t="n">
         <f aca="false">SUM(C115:I115)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15996,31 +16288,31 @@
         <v>53</v>
       </c>
       <c r="C116" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A116,'Loss time 19-10'!$G$3:$G$40,C$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A116,'Loss time 19-10'!$G$3:$G$42,C$112)</f>
         <v>0</v>
       </c>
       <c r="D116" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A116,'Loss time 19-10'!$G$3:$G$40,D$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A116,'Loss time 19-10'!$G$3:$G$42,D$112)</f>
         <v>0</v>
       </c>
       <c r="E116" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A116,'Loss time 19-10'!$G$3:$G$40,E$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A116,'Loss time 19-10'!$G$3:$G$42,E$112)</f>
         <v>31.5</v>
       </c>
       <c r="F116" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A116,'Loss time 19-10'!$G$3:$G$40,F$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A116,'Loss time 19-10'!$G$3:$G$42,F$112)</f>
         <v>157.5</v>
       </c>
       <c r="G116" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A116,'Loss time 19-10'!$G$3:$G$40,G$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A116,'Loss time 19-10'!$G$3:$G$42,G$112)</f>
         <v>0</v>
       </c>
       <c r="H116" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A116,'Loss time 19-10'!$G$3:$G$40,H$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A116,'Loss time 19-10'!$G$3:$G$42,H$112)</f>
         <v>63</v>
       </c>
       <c r="I116" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$40,'Loss time 19-10'!$H$3:$H$40,$A116,'Loss time 19-10'!$G$3:$G$40,I$112)</f>
+        <f aca="false">SUMIFS('Loss time 19-10'!$Q$3:$Q$42,'Loss time 19-10'!$H$3:$H$42,$A116,'Loss time 19-10'!$G$3:$G$42,I$112)</f>
         <v>0</v>
       </c>
       <c r="J116" s="24" t="n">
@@ -16043,11 +16335,11 @@
       </c>
       <c r="E117" s="24" t="n">
         <f aca="false">SUM(E113:E116)</f>
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F117" s="24" t="n">
         <f aca="false">SUM(F113:F116)</f>
-        <v>207.5</v>
+        <v>223.5</v>
       </c>
       <c r="G117" s="24" t="n">
         <f aca="false">SUM(G113:G116)</f>
@@ -16063,12 +16355,12 @@
       </c>
       <c r="J117" s="24" t="n">
         <f aca="false">SUM(J113:J116)</f>
-        <v>524</v>
+        <v>548</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="18" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16076,7 +16368,7 @@
         <v>8</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>18</v>
@@ -16097,7 +16389,7 @@
         <v>72</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>75</v>
@@ -16111,31 +16403,31 @@
         <v>20</v>
       </c>
       <c r="C122" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A122,'Loss time 20-10'!$G$3:$G$39,C$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A122,'Loss time 20-10'!$G$3:$G$43,C$121)</f>
         <v>3.5</v>
       </c>
       <c r="D122" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A122,'Loss time 20-10'!$G$3:$G$39,D$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A122,'Loss time 20-10'!$G$3:$G$43,D$121)</f>
         <v>9</v>
       </c>
       <c r="E122" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A122,'Loss time 20-10'!$G$3:$G$39,E$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A122,'Loss time 20-10'!$G$3:$G$43,E$121)</f>
         <v>9.5</v>
       </c>
       <c r="F122" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A122,'Loss time 20-10'!$G$3:$G$39,F$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A122,'Loss time 20-10'!$G$3:$G$43,F$121)</f>
         <v>25</v>
       </c>
       <c r="G122" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A122,'Loss time 20-10'!$G$3:$G$39,G$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A122,'Loss time 20-10'!$G$3:$G$43,G$121)</f>
         <v>0</v>
       </c>
       <c r="H122" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A122,'Loss time 20-10'!$G$3:$G$39,H$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A122,'Loss time 20-10'!$G$3:$G$43,H$121)</f>
         <v>0</v>
       </c>
       <c r="I122" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A122,'Loss time 20-10'!$G$3:$G$39,I$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A122,'Loss time 20-10'!$G$3:$G$43,I$121)</f>
         <v>0</v>
       </c>
       <c r="J122" s="24" t="n">
@@ -16151,31 +16443,31 @@
         <v>31</v>
       </c>
       <c r="C123" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A123,'Loss time 20-10'!$G$3:$G$39,C$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A123,'Loss time 20-10'!$G$3:$G$43,C$121)</f>
         <v>12.5</v>
       </c>
       <c r="D123" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A123,'Loss time 20-10'!$G$3:$G$39,D$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A123,'Loss time 20-10'!$G$3:$G$43,D$121)</f>
         <v>112.5</v>
       </c>
       <c r="E123" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A123,'Loss time 20-10'!$G$3:$G$39,E$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A123,'Loss time 20-10'!$G$3:$G$43,E$121)</f>
         <v>75</v>
       </c>
       <c r="F123" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A123,'Loss time 20-10'!$G$3:$G$39,F$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A123,'Loss time 20-10'!$G$3:$G$43,F$121)</f>
         <v>25</v>
       </c>
       <c r="G123" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A123,'Loss time 20-10'!$G$3:$G$39,G$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A123,'Loss time 20-10'!$G$3:$G$43,G$121)</f>
         <v>0</v>
       </c>
       <c r="H123" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A123,'Loss time 20-10'!$G$3:$G$39,H$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A123,'Loss time 20-10'!$G$3:$G$43,H$121)</f>
         <v>0</v>
       </c>
       <c r="I123" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A123,'Loss time 20-10'!$G$3:$G$39,I$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A123,'Loss time 20-10'!$G$3:$G$43,I$121)</f>
         <v>0</v>
       </c>
       <c r="J123" s="24" t="n">
@@ -16191,36 +16483,36 @@
         <v>49</v>
       </c>
       <c r="C124" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A124,'Loss time 20-10'!$G$3:$G$39,C$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A124,'Loss time 20-10'!$G$3:$G$43,C$121)</f>
         <v>0</v>
       </c>
       <c r="D124" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A124,'Loss time 20-10'!$G$3:$G$39,D$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A124,'Loss time 20-10'!$G$3:$G$43,D$121)</f>
         <v>0</v>
       </c>
       <c r="E124" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A124,'Loss time 20-10'!$G$3:$G$39,E$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A124,'Loss time 20-10'!$G$3:$G$43,E$121)</f>
+        <v>16</v>
+      </c>
+      <c r="F124" s="23" t="n">
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A124,'Loss time 20-10'!$G$3:$G$43,F$121)</f>
+        <v>32</v>
+      </c>
+      <c r="G124" s="23" t="n">
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A124,'Loss time 20-10'!$G$3:$G$43,G$121)</f>
         <v>0</v>
       </c>
-      <c r="F124" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A124,'Loss time 20-10'!$G$3:$G$39,F$121)</f>
+      <c r="H124" s="23" t="n">
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A124,'Loss time 20-10'!$G$3:$G$43,H$121)</f>
         <v>0</v>
       </c>
-      <c r="G124" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A124,'Loss time 20-10'!$G$3:$G$39,G$121)</f>
-        <v>0</v>
-      </c>
-      <c r="H124" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A124,'Loss time 20-10'!$G$3:$G$39,H$121)</f>
-        <v>0</v>
-      </c>
       <c r="I124" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A124,'Loss time 20-10'!$G$3:$G$39,I$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A124,'Loss time 20-10'!$G$3:$G$43,I$121)</f>
         <v>0</v>
       </c>
       <c r="J124" s="24" t="n">
         <f aca="false">SUM(C124:I124)</f>
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16231,36 +16523,36 @@
         <v>53</v>
       </c>
       <c r="C125" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A125,'Loss time 20-10'!$G$3:$G$39,C$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A125,'Loss time 20-10'!$G$3:$G$43,C$121)</f>
         <v>0</v>
       </c>
       <c r="D125" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A125,'Loss time 20-10'!$G$3:$G$39,D$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A125,'Loss time 20-10'!$G$3:$G$43,D$121)</f>
         <v>0</v>
       </c>
       <c r="E125" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A125,'Loss time 20-10'!$G$3:$G$39,E$121)</f>
-        <v>31.5</v>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A125,'Loss time 20-10'!$G$3:$G$43,E$121)</f>
+        <v>36</v>
       </c>
       <c r="F125" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A125,'Loss time 20-10'!$G$3:$G$39,F$121)</f>
-        <v>130.5</v>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A125,'Loss time 20-10'!$G$3:$G$43,F$121)</f>
+        <v>139.5</v>
       </c>
       <c r="G125" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A125,'Loss time 20-10'!$G$3:$G$39,G$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A125,'Loss time 20-10'!$G$3:$G$43,G$121)</f>
         <v>0</v>
       </c>
       <c r="H125" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A125,'Loss time 20-10'!$G$3:$G$39,H$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A125,'Loss time 20-10'!$G$3:$G$43,H$121)</f>
         <v>63</v>
       </c>
       <c r="I125" s="23" t="n">
-        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$39,'Loss time 20-10'!$H$3:$H$39,$A125,'Loss time 20-10'!$G$3:$G$39,I$121)</f>
+        <f aca="false">SUMIFS('Loss time 20-10'!$Q$3:$Q$43,'Loss time 20-10'!$H$3:$H$43,$A125,'Loss time 20-10'!$G$3:$G$43,I$121)</f>
         <v>0</v>
       </c>
       <c r="J125" s="24" t="n">
         <f aca="false">SUM(C125:I125)</f>
-        <v>225</v>
+        <v>238.5</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16278,11 +16570,11 @@
       </c>
       <c r="E126" s="24" t="n">
         <f aca="false">SUM(E122:E125)</f>
-        <v>116</v>
+        <v>136.5</v>
       </c>
       <c r="F126" s="24" t="n">
         <f aca="false">SUM(F122:F125)</f>
-        <v>180.5</v>
+        <v>221.5</v>
       </c>
       <c r="G126" s="24" t="n">
         <f aca="false">SUM(G122:G125)</f>
@@ -16298,12 +16590,12 @@
       </c>
       <c r="J126" s="24" t="n">
         <f aca="false">SUM(J122:J125)</f>
-        <v>497</v>
+        <v>558.5</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="20" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -16322,7 +16614,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -16334,348 +16626,348 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>48</v>
+        <v>272</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P4" s="8" t="s">
         <v>272</v>
       </c>
       <c r="Q4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="R4" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,20),12,11)</f>
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,20),12,11)</f>
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="R4" s="26" t="n">
+      <c r="B6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,19),12,11)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,19),12,11)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="R8" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,16),12,11)</f>
         <v>46325</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="R5" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,15),12,11)</f>
-        <v>46324</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="R6" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,14),12,11)</f>
-        <v>46323</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="R7" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,13),12,11)</f>
-        <v>46322</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="R8" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,13),12,11)</f>
-        <v>46322</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16683,46 +16975,46 @@
         <v>278</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K9" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M9" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="L9" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>272</v>
-      </c>
       <c r="N9" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P9" s="8" t="s">
         <v>277</v>
@@ -16731,8 +17023,8 @@
         <v>279</v>
       </c>
       <c r="R9" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,13),12,11)</f>
-        <v>46322</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,15),12,11)</f>
+        <v>46324</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16743,40 +17035,40 @@
         <v>28</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J10" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>272</v>
-      </c>
       <c r="M10" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>277</v>
@@ -16788,65 +17080,65 @@
         <v>281</v>
       </c>
       <c r="R10" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,12),12,11)</f>
-        <v>46321</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,14),12,11)</f>
+        <v>46323</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J11" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>271</v>
-      </c>
       <c r="L11" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="R11" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,12),12,11)</f>
-        <v>46321</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,13),12,11)</f>
+        <v>46322</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16854,56 +17146,56 @@
         <v>282</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>48</v>
+        <v>272</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>272</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>273</v>
+        <v>48</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M12" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="N12" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="O12" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="P12" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="P12" s="8" t="s">
+      <c r="Q12" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="Q12" s="8" t="s">
-        <v>284</v>
-      </c>
       <c r="R12" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,9),12,11)</f>
-        <v>46318</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,13),12,11)</f>
+        <v>46322</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16911,232 +17203,232 @@
         <v>282</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>48</v>
+        <v>272</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>272</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>273</v>
+        <v>48</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M13" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="N13" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="N13" s="8" t="s">
+      <c r="O13" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="O13" s="8" t="s">
+      <c r="P13" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="P13" s="8" t="s">
+      <c r="Q13" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="Q13" s="8" t="s">
+      <c r="R13" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,13),12,11)</f>
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="R13" s="26" t="n">
+      <c r="B14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,12),12,11)</f>
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,12),12,11)</f>
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="R16" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,9),12,11)</f>
         <v>46318</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="R14" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,8),12,11)</f>
-        <v>46317</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="R15" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,8),12,11)</f>
-        <v>46317</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="R16" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,7),12,11)</f>
-        <v>46316</v>
-      </c>
-    </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>72</v>
@@ -17145,25 +17437,25 @@
         <v>2</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F17" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>272</v>
-      </c>
       <c r="I17" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>277</v>
@@ -17178,17 +17470,17 @@
         <v>283</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q17" s="8" t="s">
         <v>288</v>
       </c>
       <c r="R17" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,7),12,11)</f>
-        <v>46316</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,9),12,11)</f>
+        <v>46318</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17196,28 +17488,28 @@
         <v>289</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E18" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>272</v>
-      </c>
       <c r="H18" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>277</v>
@@ -17232,10 +17524,10 @@
         <v>283</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P18" s="8" t="s">
         <v>288</v>
@@ -17244,8 +17536,8 @@
         <v>290</v>
       </c>
       <c r="R18" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,6),12,11)</f>
-        <v>46315</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,8),12,11)</f>
+        <v>46317</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17253,28 +17545,28 @@
         <v>289</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E19" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>272</v>
-      </c>
       <c r="H19" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>277</v>
@@ -17289,10 +17581,10 @@
         <v>283</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P19" s="8" t="s">
         <v>288</v>
@@ -17301,65 +17593,65 @@
         <v>290</v>
       </c>
       <c r="R19" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,6),12,11)</f>
-        <v>46315</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,8),12,11)</f>
+        <v>46317</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E20" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>271</v>
-      </c>
       <c r="G20" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="R20" s="26" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,6),12,11)</f>
-        <v>46315</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,7),12,11)</f>
+        <v>46316</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17367,25 +17659,25 @@
         <v>291</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D21" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>272</v>
-      </c>
       <c r="G21" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>277</v>
@@ -17400,10 +17692,10 @@
         <v>283</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O21" s="8" t="s">
         <v>288</v>
@@ -17415,236 +17707,236 @@
         <v>292</v>
       </c>
       <c r="R21" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,7),12,11)</f>
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,6),12,11)</f>
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q23" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,6),12,11)</f>
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,6),12,11)</f>
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="O25" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="P25" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q25" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="R25" s="26" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),12,11)</f>
         <v>46314</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="M22" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="O22" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="P22" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q22" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="R22" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
-        <v>46308</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="M23" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="O23" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="P23" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q23" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="R23" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),2,11)</f>
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="M24" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="N24" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="O24" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="P24" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q24" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="R24" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
-        <v>46308</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="J25" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="M25" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="N25" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="O25" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="P25" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q25" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="R25" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
-        <v>46308</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17655,53 +17947,53 @@
         <v>28</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="O26" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P26" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q26" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="R26" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),6,11)</f>
-        <v>46307</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
+        <v>46308</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17709,56 +18001,56 @@
         <v>298</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="K27" s="13" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="L27" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="O27" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P27" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q27" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="R27" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
-        <v>46308</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),2,11)</f>
+        <v>46302</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17766,52 +18058,52 @@
         <v>299</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="L28" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="O28" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P28" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q28" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="R28" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -17820,169 +18112,169 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E29" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="H29" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="I29" s="13" t="s">
         <v>290</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>292</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>292</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N29" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P29" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q29" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="R29" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),2,11)</f>
-        <v>46302</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
+        <v>46308</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M30" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="O30" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q30" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="R30" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
-        <v>46308</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),6,11)</f>
+        <v>46307</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="O31" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P31" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q31" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="R31" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -17991,55 +18283,55 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N32" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="O32" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P32" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q32" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="R32" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -18048,112 +18340,112 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="F33" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>281</v>
-      </c>
       <c r="G33" s="13" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="O33" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P33" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q33" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="R33" s="27" t="n">
-        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
-        <v>46308</v>
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),2,11)</f>
+        <v>46302</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M34" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N34" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="O34" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P34" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q34" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="R34" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -18165,52 +18457,52 @@
         <v>300</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="K35" s="13" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="L35" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="M35" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N35" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="O35" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P35" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q35" s="13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="R35" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
@@ -18219,136 +18511,344 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="K36" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="L36" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="M36" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="N36" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="O36" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="P36" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q36" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="R36" s="27" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="K37" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="L37" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="M37" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="N37" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="O37" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="P37" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q37" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="R37" s="27" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="K38" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="L38" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="M38" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="N38" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="O38" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="P38" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q38" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="R38" s="27" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="K39" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="L39" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="M39" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="N39" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="O39" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="P39" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q39" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="R39" s="27" t="n">
+        <f aca="false">WORKDAY.INTL(DATE(2026,10,5),7,11)</f>
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="B40" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="13" t="n">
+      <c r="C40" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="F36" s="13" t="s">
+      <c r="D40" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="E40" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="H36" s="13" t="s">
+      <c r="F40" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="I36" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="K36" s="13" t="s">
+      <c r="G40" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="I40" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="L36" s="13" t="s">
+      <c r="J40" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="M36" s="13" t="s">
+      <c r="K40" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="N36" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="O36" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="P36" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q36" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="R36" s="27" t="n">
+      <c r="L40" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="M40" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="N40" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="O40" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="P40" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q40" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="R40" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),8,11)</f>
         <v>46309</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="M41" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="J37" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="K37" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="L37" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="M37" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="N37" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="O37" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="P37" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q37" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="R37" s="27" t="n">
+      <c r="N41" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="O41" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="P41" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q41" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="R41" s="27" t="n">
         <f aca="false">WORKDAY.INTL(DATE(2026,10,5),8,11)</f>
         <v>46309</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="20" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="20" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="20" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="20" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18369,6 +18869,26 @@
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
         <v>308</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="20" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="20" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="20" t="s">
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -18387,7 +18907,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -18398,62 +18918,62 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>28</v>
@@ -18516,7 +19036,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>28</v>
@@ -18579,7 +19099,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>72</v>
@@ -18642,7 +19162,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>25</v>
@@ -18705,7 +19225,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>28</v>
@@ -18768,7 +19288,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>72</v>
@@ -18831,7 +19351,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>72</v>
@@ -18894,7 +19414,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>25</v>
@@ -18957,7 +19477,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>28</v>
@@ -19020,7 +19540,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>72</v>
@@ -19083,7 +19603,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>28</v>
@@ -19146,7 +19666,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>72</v>
@@ -19209,7 +19729,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>28</v>
@@ -19272,7 +19792,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>72</v>
@@ -19335,7 +19855,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>25</v>
@@ -19398,7 +19918,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>28</v>
@@ -19461,7 +19981,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>28</v>
@@ -19524,7 +20044,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>28</v>
@@ -19585,9 +20105,261 @@
         <v>46325</v>
       </c>
     </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="28" t="n">
+        <f aca="false">DATE(2026,10,19)</f>
+        <v>46314</v>
+      </c>
+      <c r="E22" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(D22,1,11)</f>
+        <v>46315</v>
+      </c>
+      <c r="F22" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(E22,1,11)</f>
+        <v>46316</v>
+      </c>
+      <c r="G22" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(F22,1,11)</f>
+        <v>46317</v>
+      </c>
+      <c r="H22" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(G22,1,11)</f>
+        <v>46318</v>
+      </c>
+      <c r="I22" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(H22,1,11)</f>
+        <v>46319</v>
+      </c>
+      <c r="J22" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(I22,1,11)</f>
+        <v>46321</v>
+      </c>
+      <c r="K22" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(J22,1,11)</f>
+        <v>46322</v>
+      </c>
+      <c r="L22" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(K22,1,11)</f>
+        <v>46323</v>
+      </c>
+      <c r="M22" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(L22,1,11)</f>
+        <v>46324</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(M22,1,11)</f>
+        <v>46325</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(N22,1,11)</f>
+        <v>46326</v>
+      </c>
+      <c r="P22" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(O22,1,11)</f>
+        <v>46328</v>
+      </c>
+    </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
-        <v>311</v>
+      <c r="A23" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="28" t="n">
+        <f aca="false">DATE(2026,10,19)</f>
+        <v>46314</v>
+      </c>
+      <c r="E23" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(D23,1,11)</f>
+        <v>46315</v>
+      </c>
+      <c r="F23" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(E23,1,11)</f>
+        <v>46316</v>
+      </c>
+      <c r="G23" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(F23,1,11)</f>
+        <v>46317</v>
+      </c>
+      <c r="H23" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(G23,1,11)</f>
+        <v>46318</v>
+      </c>
+      <c r="I23" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(H23,1,11)</f>
+        <v>46319</v>
+      </c>
+      <c r="J23" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(I23,1,11)</f>
+        <v>46321</v>
+      </c>
+      <c r="K23" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(J23,1,11)</f>
+        <v>46322</v>
+      </c>
+      <c r="L23" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(K23,1,11)</f>
+        <v>46323</v>
+      </c>
+      <c r="M23" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(L23,1,11)</f>
+        <v>46324</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(M23,1,11)</f>
+        <v>46325</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(N23,1,11)</f>
+        <v>46326</v>
+      </c>
+      <c r="P23" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(O23,1,11)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="28" t="n">
+        <f aca="false">DATE(2026,10,20)</f>
+        <v>46315</v>
+      </c>
+      <c r="E24" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(D24,1,11)</f>
+        <v>46316</v>
+      </c>
+      <c r="F24" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(E24,1,11)</f>
+        <v>46317</v>
+      </c>
+      <c r="G24" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(F24,1,11)</f>
+        <v>46318</v>
+      </c>
+      <c r="H24" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(G24,1,11)</f>
+        <v>46319</v>
+      </c>
+      <c r="I24" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(H24,1,11)</f>
+        <v>46321</v>
+      </c>
+      <c r="J24" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(I24,1,11)</f>
+        <v>46322</v>
+      </c>
+      <c r="K24" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(J24,1,11)</f>
+        <v>46323</v>
+      </c>
+      <c r="L24" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(K24,1,11)</f>
+        <v>46324</v>
+      </c>
+      <c r="M24" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(L24,1,11)</f>
+        <v>46325</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(M24,1,11)</f>
+        <v>46326</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(N24,1,11)</f>
+        <v>46328</v>
+      </c>
+      <c r="P24" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(O24,1,11)</f>
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="28" t="n">
+        <f aca="false">DATE(2026,10,20)</f>
+        <v>46315</v>
+      </c>
+      <c r="E25" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(D25,1,11)</f>
+        <v>46316</v>
+      </c>
+      <c r="F25" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(E25,1,11)</f>
+        <v>46317</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(F25,1,11)</f>
+        <v>46318</v>
+      </c>
+      <c r="H25" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(G25,1,11)</f>
+        <v>46319</v>
+      </c>
+      <c r="I25" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(H25,1,11)</f>
+        <v>46321</v>
+      </c>
+      <c r="J25" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(I25,1,11)</f>
+        <v>46322</v>
+      </c>
+      <c r="K25" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(J25,1,11)</f>
+        <v>46323</v>
+      </c>
+      <c r="L25" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(K25,1,11)</f>
+        <v>46324</v>
+      </c>
+      <c r="M25" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(L25,1,11)</f>
+        <v>46325</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(M25,1,11)</f>
+        <v>46326</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(N25,1,11)</f>
+        <v>46328</v>
+      </c>
+      <c r="P25" s="28" t="n">
+        <f aca="false">WORKDAY.INTL(O25,1,11)</f>
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>
